--- a/ig/travaux-tru/StructureDefinition-sdo-task.xlsx
+++ b/ig/travaux-tru/StructureDefinition-sdo-task.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/sdo-esms/sdo-task</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sdo/StructureDefinition/sdo-task</t>
   </si>
   <si>
     <t>Version</t>
